--- a/data/gravel/BMC URS 01 2024.xlsx
+++ b/data/gravel/BMC URS 01 2024.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51C2DAF1-5075-014F-915F-43A70D0468B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{636B0674-0CC6-DC47-9CF3-C967CFA0B3DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="760" yWindow="1280" windowWidth="23980" windowHeight="13680" xr2:uid="{AE0F04AA-80E5-8247-9791-D6B95FAD9AB5}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="118">
   <si>
     <t>brand</t>
   </si>
@@ -994,6 +994,9 @@
       <c r="P7" s="1" t="s">
         <v>7</v>
       </c>
+      <c r="Q7" s="1" t="s">
+        <v>114</v>
+      </c>
       <c r="T7" s="1" t="s">
         <v>115</v>
       </c>
